--- a/database/controller_excel/Resguardo_.xlsx
+++ b/database/controller_excel/Resguardo_.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="32">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,25 +38,22 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>14/07/2025</t>
+    <t>15/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>TI</t>
+    <t>ds</t>
   </si>
   <si>
     <t>Región:</t>
   </si>
   <si>
-    <t>Sur</t>
+    <t>Norte</t>
   </si>
   <si>
     <t>Ubicación:</t>
-  </si>
-  <si>
-    <t>Base Operativa</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -920,7 +917,7 @@
         <v>12</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
@@ -929,7 +926,7 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
@@ -978,24 +975,24 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="D16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="E16" s="39" t="s">
         <v>17</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>18</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J16" s="40"/>
       <c r="K16" s="17"/>
@@ -1021,7 +1018,7 @@
       <c r="C18" s="24"/>
       <c r="D18" s="24"/>
       <c r="E18" s="54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F18" s="31"/>
       <c r="G18" s="35"/>
@@ -1056,7 +1053,7 @@
     <row r="21" spans="1:11" customHeight="1" ht="15.75">
       <c r="A21" s="19"/>
       <c r="B21" s="33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" s="26"/>
       <c r="D21" s="26"/>
@@ -1082,7 +1079,7 @@
     <row r="23" spans="1:11" customHeight="1" ht="15.75">
       <c r="A23" s="20"/>
       <c r="B23" s="27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="26"/>
       <c r="D23" s="26"/>
@@ -1096,7 +1093,7 @@
     <row r="24" spans="1:11" customHeight="1" ht="15">
       <c r="A24" s="20"/>
       <c r="B24" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="26"/>
@@ -1110,7 +1107,7 @@
     <row r="25" spans="1:11" customHeight="1" ht="15">
       <c r="A25" s="20"/>
       <c r="B25" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="26"/>
       <c r="D25" s="26"/>
@@ -1124,7 +1121,7 @@
     <row r="26" spans="1:11" customHeight="1" ht="15">
       <c r="A26" s="20"/>
       <c r="B26" s="27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="26"/>
       <c r="D26" s="26"/>
@@ -1138,7 +1135,7 @@
     <row r="27" spans="1:11" customHeight="1" ht="15">
       <c r="A27" s="20"/>
       <c r="B27" s="27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" s="26"/>
       <c r="D27" s="26"/>
@@ -1164,7 +1161,7 @@
     <row r="29" spans="1:11" customHeight="1" ht="27.75">
       <c r="A29" s="17"/>
       <c r="B29" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
@@ -1196,12 +1193,12 @@
       <c r="A32" s="22"/>
       <c r="B32" s="22"/>
       <c r="C32" s="25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
       <c r="H32" s="34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I32" s="26"/>
       <c r="J32" s="26"/>
@@ -1218,7 +1215,7 @@
     <row r="35" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="36" spans="1:11" customHeight="1" ht="15.75">
       <c r="C36" s="25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
@@ -1231,7 +1228,7 @@
     </row>
     <row r="37" spans="1:11" customHeight="1" ht="15.75">
       <c r="C37" s="25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
